--- a/notebooks/andel_landsdeler_2014_2026/data/prosjekter.xlsx
+++ b/notebooks/andel_landsdeler_2014_2026/data/prosjekter.xlsx
@@ -5,14 +5,16 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="prosjekter" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="prosjekter_korrigert" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Utregninger opprinnelig" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Utregninger korrigert" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="gillesvik" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="prosjekter_2010_2026_sammenstil" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Utregninger opprinnelig" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Utregninger korrigert" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="gillesvik" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Sheet7" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="281">
   <si>
     <t xml:space="preserve">virksomhet</t>
   </si>
@@ -434,7 +436,7 @@
     <t xml:space="preserve">MVA justering</t>
   </si>
   <si>
-    <t xml:space="preserve">Geografisk korr</t>
+    <t xml:space="preserve">Geografisk vekting</t>
   </si>
   <si>
     <t xml:space="preserve">stat</t>
@@ -455,6 +457,27 @@
     <t xml:space="preserve">Trolig uten MVA, må multipliseres</t>
   </si>
   <si>
+    <t xml:space="preserve">Utdrag fra andre regneark!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_korrigert_2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bygges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINOR</t>
+  </si>
+  <si>
     <t xml:space="preserve">BEFOLKNINGSANDEL 2025 (SSB 06912)</t>
   </si>
   <si>
@@ -495,20 +518,373 @@
   </si>
   <si>
     <t xml:space="preserve">Per Areal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Åpningsår</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leverandør</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fylke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antall km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prognose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostn. ramme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">År for prognose/kostn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statlig andel %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moms-justering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ByggKPI mult år-&gt;2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUM i 2026 kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUM_stat_2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUM_stat_2026_svar_statsråd_2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merknad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E18 Krosby-Knapstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Østfold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ØST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bompengeandel iht "Østfoldpakka"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVV årsrapport 2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVV årsrapport 2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St.prp. nr. 79 - regjeringen.no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E18 Bjørvikatunnelen (opera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oslo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">E18 Bjørvikatunnelen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St.prp. nr. 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6 Skaberudkrysset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hedmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E39 Stangeland-Sandved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogaland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VEST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rv 13 Bugjelet-Brimnes (rassikring, byggetrinn 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hordaland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6 Nordre avlastningsveg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sør-Trøndelag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIDT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E39 Renndalen-Staurset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M&amp;R/Trøndelag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Er vel 99% i Trøndelag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6 MajaHaugen-Flygum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nordland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rv. 70 Freifjordtunnelen (rehab.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Møre og Romsdal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bybanen/Bergen (byggetrinn 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude AI Sonnet 4.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6 Dal-Minnesund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akershus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude AI Sonnet 4.6 (mai 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E 16 Seltun-Stuvane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sogn og fj.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E39 Børtveit-Steinnestunnelen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rv 80 Røvika-Strømsnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lysaker-Sandvika dobbelspor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oslo/Akershus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dobbelspor Barkåker-Tønsberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vestfold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gevingåsen tunnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E18 Sky – Langangen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vestfold/Telemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E16 Nestunnelen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buskerud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Rv 510 Solasplitten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E39 Nyborgkrysset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E39 Torvund – Teigen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E39 Kvivsvegen i Sogn og Fj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sogn og fj. + M&amp;R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opprinnelig var det meningen at prosjektet skulle være delvis bompengefinansiert, men Samferdselsdepartementet bestemte at alt skulle finansieres med bevilgninger over statsbudsjettet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rv 706 Dortealyst – Stavne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sør Trøndelag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rv 70 Brunneset – Øygarden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6 Øyer - Tretten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oppland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Åpnet desember 2012, planlagt åpning var i 2013 (ikke i SVV doc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E39 Astad – Knutset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://anlegg.bygg.no/bygg/her-kan-du-kjore-nye-e39/502482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rv 9 Krokå – Langeid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aust Agder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SØR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rv 7 Hardangerbrua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menons rapport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rv 7 Bugjelet – Brimnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rv 13 Tysdalsvatnet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E16 Omlegging forbi Voss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E39 Knutset – Høgset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6 Sentervegen – Tonstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miljøpakke Trondheim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rv 150 Ulvensplitten – Sinsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6 Værnes – Kvithammar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nord Tr.lag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(kombinert med Nidelv bru blir det 4 mrd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6 Harran – Nes bru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rv 80 Løding – Vikan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E105 Storskog – Elvenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finnmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utbedring, trolig lav pris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.ifinnmark.no/sorsia/veisprekk-pa-15-mill/s/1-65-6955927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6 Møllnes – Kvenvik </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="0.00"/>
+    <numFmt numFmtId="170" formatCode="@"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -604,6 +980,11 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
@@ -629,8 +1010,15 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,6 +1029,48 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFD7"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFBBE33D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE33D"/>
+        <bgColor rgb="FF81D41A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE994"/>
+        <bgColor rgb="FFFFFFD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBF00"/>
+        <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FFBBE33D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50938A"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
   </fills>
@@ -678,7 +1108,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -687,15 +1117,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -743,7 +1173,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -752,22 +1210,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -775,24 +1257,28 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -815,7 +1301,7 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FFA7074B"/>
@@ -832,7 +1318,7 @@
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFBBE33D"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
@@ -841,21 +1327,21 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFE994"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFF7D1D5"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FF81D41A"/>
+      <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF4000"/>
       <rgbColor rgb="FF3465A4"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF00A933"/>
+      <rgbColor rgb="FF50938A"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FFBE480A"/>
@@ -878,9 +1364,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>244440</xdr:colOff>
+      <xdr:colOff>244080</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>83880</xdr:rowOff>
+      <xdr:rowOff>83520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -894,7 +1380,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9442080" y="3304080"/>
-          <a:ext cx="7550640" cy="4163760"/>
+          <a:ext cx="7550280" cy="4163400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -920,9 +1406,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>235440</xdr:colOff>
+      <xdr:colOff>235080</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>99360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -936,7 +1422,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="812880" y="325080"/>
-          <a:ext cx="7550640" cy="4163760"/>
+          <a:ext cx="7550280" cy="4163400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1075,7 +1561,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="63.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20.24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4072,14 +4558,15 @@
   <dimension ref="A1:P102"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="45.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="66.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="30.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16.69"/>
@@ -8477,6 +8964,1729 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E106"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="76.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>4556</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>5737</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>4226</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>3310</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>3917</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>7772</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E57" s="0" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E58" s="0" t="n">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E59" s="0" t="n">
+        <v>3356</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E60" s="0" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E62" s="0" t="n">
+        <v>6849</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E63" s="0" t="n">
+        <v>3242</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64" s="1"/>
+      <c r="E64" s="0" t="n">
+        <v>3718</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" s="1"/>
+      <c r="E65" s="0" t="n">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="1"/>
+      <c r="E66" s="0" t="n">
+        <v>3492</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D67" s="1"/>
+      <c r="E67" s="0" t="n">
+        <v>16093</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D68" s="1"/>
+      <c r="E68" s="0" t="n">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D69" s="1"/>
+      <c r="E69" s="0" t="n">
+        <v>6527</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D70" s="1"/>
+      <c r="E70" s="0" t="n">
+        <v>21893</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D71" s="1"/>
+      <c r="E71" s="0" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D72" s="1"/>
+      <c r="E72" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="0" t="n">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="0" t="n">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D75" s="1"/>
+      <c r="E75" s="0" t="n">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D76" s="1"/>
+      <c r="E76" s="0" t="n">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D77" s="1"/>
+      <c r="E77" s="0" t="n">
+        <v>7205</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D78" s="1"/>
+      <c r="E78" s="0" t="n">
+        <v>11334</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D79" s="1"/>
+      <c r="E79" s="0" t="n">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D80" s="1"/>
+      <c r="E80" s="0" t="n">
+        <v>37749</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E81" s="0" t="n">
+        <v>6233</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E82" s="0" t="n">
+        <v>8684</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E83" s="0" t="n">
+        <v>2735</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D84" s="1"/>
+      <c r="E84" s="0" t="n">
+        <v>5126</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D85" s="1"/>
+      <c r="E85" s="0" t="n">
+        <v>22290</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D86" s="1"/>
+      <c r="E86" s="0" t="n">
+        <v>16179</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D87" s="1"/>
+      <c r="E87" s="0" t="n">
+        <v>14982</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D88" s="1"/>
+      <c r="E88" s="0" t="n">
+        <v>9729</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E89" s="0" t="n">
+        <v>7277.775</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E90" s="0" t="n">
+        <v>11114.175</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E91" s="0" t="n">
+        <v>12847.8</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E92" s="0" t="n">
+        <v>46837.5</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E93" s="0" t="n">
+        <v>7752.5</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E94" s="0" t="n">
+        <v>5930</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E95" s="0" t="n">
+        <v>3920</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E96" s="0" t="n">
+        <v>2992.5</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E97" s="0" t="n">
+        <v>16368.75</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D98" s="1"/>
+      <c r="E98" s="0" t="n">
+        <v>47775</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D99" s="1"/>
+      <c r="E99" s="0" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D100" s="1"/>
+      <c r="E100" s="0" t="n">
+        <v>35648.75</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D101" s="1"/>
+      <c r="E101" s="0" t="n">
+        <v>13987.5</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D102" s="1"/>
+      <c r="E102" s="0" t="n">
+        <v>12073.75</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D103" s="1"/>
+      <c r="E103" s="0" t="n">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D104" s="1"/>
+      <c r="E104" s="0" t="n">
+        <v>11336.25</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D105" s="1"/>
+      <c r="E105" s="0" t="n">
+        <v>3902</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D106" s="1"/>
+      <c r="E106" s="0" t="n">
+        <v>4917</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A4:L57"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -8486,12 +10696,12 @@
   </cols>
   <sheetData>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>143</v>
+      <c r="A4" s="24" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="1" t="n">
@@ -8499,25 +10709,25 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1420000</v>
       </c>
-      <c r="C6" s="18"/>
+      <c r="C6" s="26"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="25" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>480000</v>
       </c>
-      <c r="C7" s="19"/>
+      <c r="C7" s="27"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="25" t="s">
         <v>60</v>
       </c>
       <c r="B8" s="1" t="n">
@@ -8525,7 +10735,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="25" t="s">
         <v>47</v>
       </c>
       <c r="B9" s="1" t="n">
@@ -8533,8 +10743,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>144</v>
+      <c r="A10" s="24" t="s">
+        <v>151</v>
       </c>
       <c r="B10" s="1" t="n">
         <f aca="false">SUM(B5:B9)</f>
@@ -8542,595 +10752,595 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16"/>
+      <c r="A15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>145</v>
+      <c r="A16" s="24" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>150</v>
+      <c r="A17" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="21" t="n">
+      <c r="B18" s="29" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Østlandet",prosjekter!B$2:B$101,"Ferdig")+2</f>
         <v>34</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="30" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Østlandet",prosjekter!B$2:B$101,"Ferdig")/1000 + 3.6</f>
         <v>145.071</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="31" t="n">
         <f aca="false">IFERROR(C18/$C$23,0)</f>
         <v>0.611600386173635</v>
       </c>
-      <c r="E18" s="24" t="n">
+      <c r="E18" s="32" t="n">
         <f aca="false">C18*1000000/$B$5</f>
         <v>50.5473867595819</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Vestlandet",prosjekter!B$2:B$101,"Ferdig")</f>
         <v>16</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="30" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Vestlandet",prosjekter!B$2:B$101,"Ferdig")/1000 -2.3</f>
         <v>34.264</v>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="31" t="n">
         <f aca="false">IFERROR(C19/$C$23,0)</f>
         <v>0.144452548282244</v>
       </c>
-      <c r="E19" s="24" t="n">
+      <c r="E19" s="32" t="n">
         <f aca="false">C19*1000000/$B$6</f>
         <v>24.1295774647887</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Nord-Norge",prosjekter!B$2:B$101,"Ferdig")</f>
         <v>13</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Nord-Norge",prosjekter!B$2:B$101,"Ferdig")/1000</f>
         <v>28.278</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="31" t="n">
         <f aca="false">IFERROR(C20/$C23,0)</f>
         <v>0.119216354200481</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E20" s="32" t="n">
         <f aca="false">C20*1000000/$B$7</f>
         <v>58.9125</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="29" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Sørlandet",prosjekter!B$2:B$101,"Ferdig") + 1</f>
         <v>3</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="30" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Sørlandet",prosjekter!B$2:B$101,"Ferdig")/1000 + 12.8</f>
         <v>20.452</v>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="31" t="n">
         <f aca="false">IFERROR(C21/$C$23,0)</f>
         <v>0.0862229604677929</v>
       </c>
-      <c r="E21" s="24" t="n">
+      <c r="E21" s="32" t="n">
         <f aca="false">C21*1000000/$B$8</f>
         <v>63.9125</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="29" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Trøndelag",prosjekter!B$2:B$101,"Ferdig") + 1</f>
         <v>5</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="30" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Trøndelag",prosjekter!B$2:B$101,"Ferdig")/1000 + 2.9</f>
         <v>9.134</v>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="31" t="n">
         <f aca="false">IFERROR(C22/$C$23,0)</f>
         <v>0.0385077508758469</v>
       </c>
-      <c r="E22" s="24" t="n">
+      <c r="E22" s="32" t="n">
         <f aca="false">C22*1000000/$B$9</f>
         <v>19.0291666666667</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" s="20" t="n">
+      <c r="A23" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="28" t="n">
         <f aca="false">SUM(B16:B22)</f>
         <v>71</v>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C23" s="35" t="n">
         <f aca="false">SUM(C18:C22)</f>
         <v>237.199</v>
       </c>
-      <c r="D23" s="28" t="n">
+      <c r="D23" s="36" t="n">
         <f aca="false">SUM(D18:D22)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16" t="s">
-        <v>152</v>
+      <c r="A27" s="24" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>150</v>
+      <c r="A28" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Østlandet",prosjekter!B$2:B$101,"Ferdig")</f>
         <v>32</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Østlandet",prosjekter!B$2:B$101,"Ferdig")/1000</f>
         <v>141.471</v>
       </c>
-      <c r="D29" s="23" t="n">
+      <c r="D29" s="31" t="n">
         <f aca="false">IFERROR(C29/$C$34,0)</f>
         <v>0.642468857715067</v>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="E29" s="32" t="n">
         <f aca="false">C29*1000000/$B$5</f>
         <v>49.293031358885</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Vestlandet",prosjekter!B$2:B$101,"Ferdig")</f>
         <v>16</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Vestlandet",prosjekter!B$2:B$101,"Ferdig")/1000</f>
         <v>36.564</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="31" t="n">
         <f aca="false">IFERROR(C30/$C$34,0)</f>
         <v>0.166049800407813</v>
       </c>
-      <c r="E30" s="24" t="n">
+      <c r="E30" s="32" t="n">
         <f aca="false">C30*1000000/$B$6</f>
         <v>25.7492957746479</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Nord-Norge",prosjekter!B$2:B$101,"Ferdig")</f>
         <v>13</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Nord-Norge",prosjekter!B$2:B$101,"Ferdig")/1000</f>
         <v>28.278</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D31" s="31" t="n">
         <f aca="false">IFERROR(C31/$C$34,0)</f>
         <v>0.12842020172662</v>
       </c>
-      <c r="E31" s="24" t="n">
+      <c r="E31" s="32" t="n">
         <f aca="false">C31*1000000/$B$7</f>
         <v>58.9125</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="25" t="n">
+      <c r="B32" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Sørlandet",prosjekter!B$2:B$101,"Ferdig")</f>
         <v>2</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Sørlandet",prosjekter!B$2:B$101,"Ferdig")/1000</f>
         <v>7.652</v>
       </c>
-      <c r="D32" s="23" t="n">
+      <c r="D32" s="31" t="n">
         <f aca="false">IFERROR(C32/$C$34,0)</f>
         <v>0.0347503848791321</v>
       </c>
-      <c r="E32" s="24" t="n">
+      <c r="E32" s="32" t="n">
         <f aca="false">C32*1000000/$B$8</f>
         <v>23.9125</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="25" t="n">
+      <c r="B33" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Trøndelag",prosjekter!B$2:B$101,"Ferdig")</f>
         <v>4</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Trøndelag",prosjekter!B$2:B$101,"Ferdig")/1000</f>
         <v>6.234</v>
       </c>
-      <c r="D33" s="23" t="n">
+      <c r="D33" s="31" t="n">
         <f aca="false">IFERROR(C33/$C$34,0)</f>
         <v>0.0283107552713682</v>
       </c>
-      <c r="E33" s="24" t="n">
+      <c r="E33" s="32" t="n">
         <f aca="false">C33*1000000/$B$9</f>
         <v>12.9875</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="B34" s="20" t="n">
+      <c r="A34" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" s="28" t="n">
         <f aca="false">SUM(B27:B33)</f>
         <v>67</v>
       </c>
-      <c r="C34" s="27" t="n">
+      <c r="C34" s="35" t="n">
         <f aca="false">SUM(C29:C33)</f>
         <v>220.199</v>
       </c>
-      <c r="D34" s="28" t="n">
+      <c r="D34" s="36" t="n">
         <f aca="false">SUM(D29:D33)</f>
         <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="23"/>
+      <c r="A35" s="25"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="31"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="28"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="36"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="24" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="24" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>150</v>
+      <c r="B40" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="25" t="n">
+      <c r="B41" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Østlandet")</f>
         <v>42</v>
       </c>
-      <c r="C41" s="26" t="n">
+      <c r="C41" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Østlandet")/1000</f>
         <v>232.403</v>
       </c>
-      <c r="D41" s="23" t="n">
+      <c r="D41" s="31" t="n">
         <f aca="false">IFERROR(C41/$C$46,0)</f>
         <v>0.476259078315327</v>
       </c>
-      <c r="E41" s="24" t="n">
+      <c r="E41" s="32" t="n">
         <f aca="false">C41*1000000/$B$5</f>
         <v>80.9766550522648</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B42" s="25" t="n">
+      <c r="B42" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Vestlandet")</f>
         <v>25</v>
       </c>
-      <c r="C42" s="26" t="n">
+      <c r="C42" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Vestlandet")/1000</f>
         <v>111.911</v>
       </c>
-      <c r="D42" s="23" t="n">
+      <c r="D42" s="31" t="n">
         <f aca="false">IFERROR(C42/$C$46,0)</f>
         <v>0.22933709854583</v>
       </c>
-      <c r="E42" s="24" t="n">
+      <c r="E42" s="32" t="n">
         <f aca="false">C42*1000000/$B$6</f>
         <v>78.8105633802817</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B43" s="25" t="n">
+      <c r="B43" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Nord-Norge")</f>
         <v>19</v>
       </c>
-      <c r="C43" s="26" t="n">
+      <c r="C43" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Nord-Norge")/1000</f>
         <v>71.787</v>
       </c>
-      <c r="D43" s="23" t="n">
+      <c r="D43" s="31" t="n">
         <f aca="false">IFERROR(C43/$C$46,0)</f>
         <v>0.147111743200485</v>
       </c>
-      <c r="E43" s="24" t="n">
+      <c r="E43" s="32" t="n">
         <f aca="false">C43*1000000/$B$7</f>
         <v>149.55625</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="25" t="n">
+      <c r="B44" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Sørlandet")</f>
         <v>5</v>
       </c>
-      <c r="C44" s="26" t="n">
+      <c r="C44" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Sørlandet")/1000</f>
         <v>37.688</v>
       </c>
-      <c r="D44" s="23" t="n">
+      <c r="D44" s="31" t="n">
         <f aca="false">IFERROR(C44/$C$46,0)</f>
         <v>0.0772333065560601</v>
       </c>
-      <c r="E44" s="24" t="n">
+      <c r="E44" s="32" t="n">
         <f aca="false">C44*1000000/$B$8</f>
         <v>117.775</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="25" t="n">
+      <c r="B45" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Trøndelag")</f>
         <v>7</v>
       </c>
-      <c r="C45" s="26" t="n">
+      <c r="C45" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Trøndelag")/1000</f>
         <v>34.187</v>
       </c>
-      <c r="D45" s="23" t="n">
+      <c r="D45" s="31" t="n">
         <f aca="false">IFERROR(C45/$C$46,0)</f>
         <v>0.0700587733822975</v>
       </c>
-      <c r="E45" s="24" t="n">
+      <c r="E45" s="32" t="n">
         <f aca="false">C45*1000000/$B$9</f>
         <v>71.2229166666667</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="B46" s="20" t="n">
+      <c r="A46" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B46" s="28" t="n">
         <f aca="false">SUM(B39:B45)</f>
         <v>98</v>
       </c>
-      <c r="C46" s="27" t="n">
+      <c r="C46" s="35" t="n">
         <f aca="false">SUM(C41:C45)</f>
         <v>487.976</v>
       </c>
-      <c r="D46" s="28" t="n">
+      <c r="D46" s="36" t="n">
         <f aca="false">SUM(D41:D45)</f>
         <v>1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="28" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>150</v>
+      <c r="C51" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B52" s="25" t="n">
+      <c r="B52" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Østlandet",prosjekter!B$2:B$101,"Under bygging")</f>
         <v>10</v>
       </c>
-      <c r="C52" s="26" t="n">
+      <c r="C52" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Østlandet",prosjekter!B$2:B$101,"Under bygging")/1000</f>
         <v>90.932</v>
       </c>
-      <c r="D52" s="23" t="n">
+      <c r="D52" s="31" t="n">
         <f aca="false">IFERROR(C52/$C$57,0)</f>
         <v>0.339581069322608</v>
       </c>
-      <c r="E52" s="24" t="n">
+      <c r="E52" s="32" t="n">
         <f aca="false">C52*1000000/$B$5</f>
         <v>31.6836236933798</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B53" s="25" t="n">
+      <c r="B53" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Vestlandet",prosjekter!B$2:B$101,"Under bygging")</f>
         <v>9</v>
       </c>
-      <c r="C53" s="26" t="n">
+      <c r="C53" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Vestlandet",prosjekter!B$2:B$101,"Under bygging")/1000</f>
         <v>75.347</v>
       </c>
-      <c r="D53" s="23" t="n">
+      <c r="D53" s="31" t="n">
         <f aca="false">IFERROR(C53/$C$57,0)</f>
         <v>0.28137965545958</v>
       </c>
-      <c r="E53" s="24" t="n">
+      <c r="E53" s="32" t="n">
         <f aca="false">C53*1000000/$B$6</f>
         <v>53.0612676056338</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B54" s="25" t="n">
+      <c r="B54" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Nord-Norge",prosjekter!B$2:B$101,"Under bygging")</f>
         <v>6</v>
       </c>
-      <c r="C54" s="26" t="n">
+      <c r="C54" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Nord-Norge",prosjekter!B$2:B$101,"Under bygging")/1000</f>
         <v>43.509</v>
       </c>
-      <c r="D54" s="23" t="n">
+      <c r="D54" s="31" t="n">
         <f aca="false">IFERROR(C54/$C$57,0)</f>
         <v>0.162482214678632</v>
       </c>
-      <c r="E54" s="24" t="n">
+      <c r="E54" s="32" t="n">
         <f aca="false">C54*1000000/$B$7</f>
         <v>90.64375</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="25" t="n">
+      <c r="B55" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Sørlandet",prosjekter!B$2:B$101,"Ferdig")</f>
         <v>2</v>
       </c>
-      <c r="C55" s="26" t="n">
+      <c r="C55" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Sørlandet",prosjekter!B$2:B$101,"Under bygging")/1000</f>
         <v>30.036</v>
       </c>
-      <c r="D55" s="23" t="n">
+      <c r="D55" s="31" t="n">
         <f aca="false">IFERROR(C55/$C$57,0)</f>
         <v>0.112167960653828</v>
       </c>
-      <c r="E55" s="24" t="n">
+      <c r="E55" s="32" t="n">
         <f aca="false">C55*1000000/$B$8</f>
         <v>93.8625</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="25" t="n">
+      <c r="B56" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter!I$2:I$101,"Trøndelag",prosjekter!B$2:B$101,"Under bygging")</f>
         <v>3</v>
       </c>
-      <c r="C56" s="26" t="n">
+      <c r="C56" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter!K$2:K$101,prosjekter!I$2:I$101,"Trøndelag",prosjekter!B$2:B$101,"Under bygging")/1000</f>
         <v>27.953</v>
       </c>
-      <c r="D56" s="23" t="n">
+      <c r="D56" s="31" t="n">
         <f aca="false">IFERROR(C56/$C$57,0)</f>
         <v>0.104389099885352</v>
       </c>
-      <c r="E56" s="24" t="n">
+      <c r="E56" s="32" t="n">
         <f aca="false">C56*1000000/$B$9</f>
         <v>58.2354166666667</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="B57" s="20" t="n">
+      <c r="A57" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B57" s="28" t="n">
         <f aca="false">SUM(B50:B56)</f>
         <v>30</v>
       </c>
-      <c r="C57" s="27" t="n">
+      <c r="C57" s="35" t="n">
         <f aca="false">SUM(C52:C56)</f>
         <v>267.777</v>
       </c>
-      <c r="D57" s="28" t="n">
+      <c r="D57" s="36" t="n">
         <f aca="false">SUM(D52:D56)</f>
         <v>1</v>
       </c>
@@ -9147,7 +11357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -9158,16 +11368,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="33.64"/>
   </cols>
   <sheetData>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>143</v>
+      <c r="A4" s="24" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="1" t="n">
@@ -9175,25 +11385,25 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1420000</v>
       </c>
-      <c r="C6" s="18"/>
+      <c r="C6" s="26"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="25" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>480000</v>
       </c>
-      <c r="C7" s="19"/>
+      <c r="C7" s="27"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="25" t="s">
         <v>60</v>
       </c>
       <c r="B8" s="1" t="n">
@@ -9201,7 +11411,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="25" t="s">
         <v>47</v>
       </c>
       <c r="B9" s="1" t="n">
@@ -9209,8 +11419,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>144</v>
+      <c r="A10" s="24" t="s">
+        <v>151</v>
       </c>
       <c r="B10" s="1" t="n">
         <f aca="false">SUM(B5:B9)</f>
@@ -9219,52 +11429,52 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>94585</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>57694</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>112951</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>16434</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>42201</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
-        <v>144</v>
+      <c r="A19" s="24" t="s">
+        <v>151</v>
       </c>
       <c r="B19" s="1" t="n">
         <f aca="false">SUM(B14:B18)</f>
@@ -9272,468 +11482,488 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
-        <v>152</v>
+      <c r="A25" s="24" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>150</v>
+      <c r="A26" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>157</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="25" t="n">
+      <c r="B27" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Østlandet",prosjekter_korrigert!B$2:B$102,"Ferdig")</f>
         <v>32</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Østlandet",prosjekter_korrigert!B$2:B$102,"Ferdig")/1000</f>
         <v>159.6175</v>
       </c>
-      <c r="D27" s="23" t="n">
+      <c r="D27" s="31" t="n">
         <f aca="false">IFERROR(C27/$C$32,0)</f>
         <v>0.663447470364274</v>
       </c>
-      <c r="E27" s="24" t="n">
+      <c r="E27" s="32" t="n">
         <f aca="false">C27*1000000/$B$5</f>
         <v>55.6158536585366</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" s="37" t="n">
         <f aca="false">1000 * C27 / $B14</f>
         <v>1.68755616641116</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Vestlandet",prosjekter_korrigert!B$2:B$102,"Ferdig")</f>
         <v>18</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Vestlandet",prosjekter_korrigert!B$2:B$102,"Ferdig")/1000</f>
         <v>38.541</v>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="31" t="n">
         <f aca="false">IFERROR(C28/$C$32,0)</f>
         <v>0.160195022195621</v>
       </c>
-      <c r="E28" s="24" t="n">
+      <c r="E28" s="32" t="n">
         <f aca="false">C28*1000000/$B$6</f>
         <v>27.1415492957747</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="37" t="n">
         <f aca="false">1000 * C28 / $B15</f>
         <v>0.668024404617465</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Nord-Norge",prosjekter_korrigert!B$2:B$102,"Ferdig")</f>
         <v>13</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Nord-Norge",prosjekter_korrigert!B$2:B$102,"Ferdig")/1000</f>
         <v>28.278</v>
       </c>
-      <c r="D29" s="23" t="n">
+      <c r="D29" s="31" t="n">
         <f aca="false">IFERROR(C29/$C$32,0)</f>
         <v>0.117537034266048</v>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="E29" s="32" t="n">
         <f aca="false">C29*1000000/$B$7</f>
         <v>58.9125</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="37" t="n">
         <f aca="false">1000 * C29 / $B16</f>
         <v>0.250356349213376</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Sørlandet",prosjekter_korrigert!B$2:B$102,"Ferdig")</f>
         <v>2</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Sørlandet",prosjekter_korrigert!B$2:B$102,"Ferdig")/1000</f>
         <v>7.652</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="31" t="n">
         <f aca="false">IFERROR(C30/$C$32,0)</f>
         <v>0.0318054100786407</v>
       </c>
-      <c r="E30" s="24" t="n">
+      <c r="E30" s="32" t="n">
         <f aca="false">C30*1000000/$B$8</f>
         <v>23.9125</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="37" t="n">
         <f aca="false">1000 * C30 / $B17</f>
         <v>0.465620055981502</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Trøndelag",prosjekter_korrigert!B$2:B$102,"Ferdig")</f>
         <v>4</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Trøndelag",prosjekter_korrigert!B$2:B$102,"Ferdig")/1000</f>
         <v>6.4995</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D31" s="31" t="n">
         <f aca="false">IFERROR(C31/$C$32,0)</f>
         <v>0.0270150630954162</v>
       </c>
-      <c r="E31" s="24" t="n">
+      <c r="E31" s="32" t="n">
         <f aca="false">C31*1000000/$B$9</f>
         <v>13.540625</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="37" t="n">
         <f aca="false">1000 * C31 / $B18</f>
         <v>0.154012938082036</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="B32" s="20" t="n">
+      <c r="A32" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B32" s="28" t="n">
         <f aca="false">SUM(B25:B31)</f>
         <v>69</v>
       </c>
-      <c r="C32" s="27" t="n">
+      <c r="C32" s="35" t="n">
         <f aca="false">SUM(C27:C31)</f>
         <v>240.588</v>
       </c>
-      <c r="D32" s="28" t="n">
+      <c r="D32" s="36" t="n">
         <f aca="false">SUM(D27:D31)</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="23"/>
+      <c r="A33" s="25"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="31"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="28"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="36"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="24" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>150</v>
+      <c r="B38" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="25" t="n">
+      <c r="B39" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Østlandet")</f>
         <v>43</v>
       </c>
-      <c r="C39" s="26" t="n">
+      <c r="C39" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Østlandet")/1000</f>
         <v>271.18075</v>
       </c>
-      <c r="D39" s="23" t="n">
+      <c r="D39" s="31" t="n">
         <f aca="false">IFERROR(C39/$C$44,0)</f>
         <v>0.517648692591343</v>
       </c>
-      <c r="E39" s="24" t="n">
+      <c r="E39" s="32" t="n">
         <f aca="false">C39*1000000/$B$5</f>
         <v>94.4880662020906</v>
       </c>
+      <c r="F39" s="37" t="n">
+        <f aca="false">1000 * C39 / $B14</f>
+        <v>2.86705873024264</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="25" t="n">
+      <c r="B40" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Vestlandet")</f>
         <v>27</v>
       </c>
-      <c r="C40" s="26" t="n">
+      <c r="C40" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Vestlandet")/1000</f>
         <v>113.888</v>
       </c>
-      <c r="D40" s="23" t="n">
+      <c r="D40" s="31" t="n">
         <f aca="false">IFERROR(C40/$C$44,0)</f>
         <v>0.217397342185398</v>
       </c>
-      <c r="E40" s="24" t="n">
+      <c r="E40" s="32" t="n">
         <f aca="false">C40*1000000/$B$6</f>
         <v>80.2028169014085</v>
       </c>
+      <c r="F40" s="37" t="n">
+        <f aca="false">1000 * C40 / $B15</f>
+        <v>1.9740007626443</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="25" t="n">
+      <c r="B41" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Nord-Norge")</f>
         <v>19</v>
       </c>
-      <c r="C41" s="26" t="n">
+      <c r="C41" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Nord-Norge")/1000</f>
         <v>71.787</v>
       </c>
-      <c r="D41" s="23" t="n">
+      <c r="D41" s="31" t="n">
         <f aca="false">IFERROR(C41/$C$44,0)</f>
         <v>0.137032022719366</v>
       </c>
-      <c r="E41" s="24" t="n">
+      <c r="E41" s="32" t="n">
         <f aca="false">C41*1000000/$B$7</f>
         <v>149.55625</v>
       </c>
+      <c r="F41" s="37" t="n">
+        <f aca="false">1000 * C41 / $B16</f>
+        <v>0.635558782126763</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="25" t="n">
+      <c r="B42" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Sørlandet")</f>
         <v>4</v>
       </c>
-      <c r="C42" s="26" t="n">
+      <c r="C42" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Sørlandet")/1000</f>
         <v>32.562</v>
       </c>
-      <c r="D42" s="23" t="n">
+      <c r="D42" s="31" t="n">
         <f aca="false">IFERROR(C42/$C$44,0)</f>
         <v>0.0621566122527477</v>
       </c>
-      <c r="E42" s="24" t="n">
+      <c r="E42" s="32" t="n">
         <f aca="false">C42*1000000/$B$8</f>
         <v>101.75625</v>
       </c>
+      <c r="F42" s="37" t="n">
+        <f aca="false">1000 * C42 / $B17</f>
+        <v>1.98138006571742</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="25" t="n">
+      <c r="B43" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Trøndelag")</f>
         <v>7</v>
       </c>
-      <c r="C43" s="26" t="n">
+      <c r="C43" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Trøndelag")/1000</f>
         <v>34.4525</v>
       </c>
-      <c r="D43" s="23" t="n">
+      <c r="D43" s="31" t="n">
         <f aca="false">IFERROR(C43/$C$44,0)</f>
         <v>0.0657653302511452</v>
       </c>
-      <c r="E43" s="24" t="n">
+      <c r="E43" s="32" t="n">
         <f aca="false">C43*1000000/$B$9</f>
         <v>71.7760416666667</v>
       </c>
+      <c r="F43" s="37" t="n">
+        <f aca="false">1000 * C43 / $B18</f>
+        <v>0.816390606857657</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="B44" s="20" t="n">
+      <c r="A44" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B44" s="28" t="n">
         <f aca="false">SUM(B37:B43)</f>
         <v>100</v>
       </c>
-      <c r="C44" s="27" t="n">
+      <c r="C44" s="35" t="n">
         <f aca="false">SUM(C39:C43)</f>
         <v>523.87025</v>
       </c>
-      <c r="D44" s="28" t="n">
+      <c r="D44" s="36" t="n">
         <f aca="false">SUM(D39:D43)</f>
         <v>1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" s="28" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>150</v>
+      <c r="C49" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E49" s="24" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B50" s="25" t="n">
+      <c r="B50" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Østlandet",prosjekter_korrigert!B$2:B$102,"Under bygging")</f>
         <v>11</v>
       </c>
-      <c r="C50" s="26" t="n">
+      <c r="C50" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Østlandet",prosjekter_korrigert!B$2:B$102,"Under bygging")/1000</f>
         <v>111.56325</v>
       </c>
-      <c r="D50" s="23" t="n">
+      <c r="D50" s="31" t="n">
         <f aca="false">IFERROR(C50/$C$55,0)</f>
         <v>0.393823651146516</v>
       </c>
-      <c r="E50" s="24" t="n">
+      <c r="E50" s="32" t="n">
         <f aca="false">C50*1000000/$B$5</f>
         <v>38.872212543554</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B51" s="25" t="n">
+      <c r="B51" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Vestlandet",prosjekter_korrigert!B$2:B$102,"Under bygging")</f>
         <v>9</v>
       </c>
-      <c r="C51" s="26" t="n">
+      <c r="C51" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Vestlandet",prosjekter_korrigert!B$2:B$102,"Under bygging")/1000</f>
         <v>75.347</v>
       </c>
-      <c r="D51" s="23" t="n">
+      <c r="D51" s="31" t="n">
         <f aca="false">IFERROR(C51/$C$55,0)</f>
         <v>0.265978542601946</v>
       </c>
-      <c r="E51" s="24" t="n">
+      <c r="E51" s="32" t="n">
         <f aca="false">C51*1000000/$B$6</f>
         <v>53.0612676056338</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B52" s="25" t="n">
+      <c r="B52" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Nord-Norge",prosjekter_korrigert!B$2:B$102,"Under bygging")</f>
         <v>6</v>
       </c>
-      <c r="C52" s="26" t="n">
+      <c r="C52" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Nord-Norge",prosjekter_korrigert!B$2:B$102,"Under bygging")/1000</f>
         <v>43.509</v>
       </c>
-      <c r="D52" s="23" t="n">
+      <c r="D52" s="31" t="n">
         <f aca="false">IFERROR(C52/$C$55,0)</f>
         <v>0.15358886763996</v>
       </c>
-      <c r="E52" s="24" t="n">
+      <c r="E52" s="32" t="n">
         <f aca="false">C52*1000000/$B$7</f>
         <v>90.64375</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="25" t="n">
+      <c r="B53" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Sørlandet",prosjekter_korrigert!B$2:B$102,"Ferdig")</f>
         <v>2</v>
       </c>
-      <c r="C53" s="26" t="n">
+      <c r="C53" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Sørlandet",prosjekter_korrigert!B$2:B$102,"Under bygging")/1000</f>
         <v>24.91</v>
       </c>
-      <c r="D53" s="23" t="n">
+      <c r="D53" s="31" t="n">
         <f aca="false">IFERROR(C53/$C$55,0)</f>
         <v>0.0879335009517893</v>
       </c>
-      <c r="E53" s="24" t="n">
+      <c r="E53" s="32" t="n">
         <f aca="false">C53*1000000/$B$8</f>
         <v>77.84375</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B54" s="25" t="n">
+      <c r="B54" s="33" t="n">
         <f aca="false">COUNTIFS(prosjekter_korrigert!L$2:L$102,"Trøndelag",prosjekter_korrigert!B$2:B$102,"Under bygging")</f>
         <v>3</v>
       </c>
-      <c r="C54" s="26" t="n">
+      <c r="C54" s="34" t="n">
         <f aca="false">SUMIFS(prosjekter_korrigert!P$2:P$102,prosjekter_korrigert!L$2:L$102,"Trøndelag",prosjekter_korrigert!B$2:B$102,"Under bygging")/1000</f>
         <v>27.953</v>
       </c>
-      <c r="D54" s="23" t="n">
+      <c r="D54" s="31" t="n">
         <f aca="false">IFERROR(C54/$C$55,0)</f>
         <v>0.0986754376597898</v>
       </c>
-      <c r="E54" s="24" t="n">
+      <c r="E54" s="32" t="n">
         <f aca="false">C54*1000000/$B$9</f>
         <v>58.2354166666667</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="B55" s="20" t="n">
+      <c r="A55" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B55" s="28" t="n">
         <f aca="false">SUM(B48:B54)</f>
         <v>31</v>
       </c>
-      <c r="C55" s="27" t="n">
+      <c r="C55" s="35" t="n">
         <f aca="false">SUM(C50:C54)</f>
         <v>283.28225</v>
       </c>
-      <c r="D55" s="28" t="n">
+      <c r="D55" s="36" t="n">
         <f aca="false">SUM(D50:D54)</f>
         <v>1</v>
       </c>
@@ -9749,7 +11979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -9757,7 +11987,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="131.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="131.6"/>
   </cols>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -9769,4 +11999,2382 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:U54"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="21.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="31.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="58.51"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="34.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="I1" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="J1" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T1" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="U1" s="38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="39"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+    </row>
+    <row r="5" customFormat="false" ht="27.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="39"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H5" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="38" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="J5" s="39"/>
+      <c r="K5" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L5" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="M5" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N5" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O5" s="38" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P5" s="41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="S5" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="T5" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="U5" s="42" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="22.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="39"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" s="38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I6" s="38" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="L6" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="M6" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N6" s="38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O6" s="38" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="P6" s="41" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="Q6" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="R6" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="S6" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="T6" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="U6" s="42" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="39"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" s="38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I7" s="38" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="J7" s="39"/>
+      <c r="K7" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="L7" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="M7" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N7" s="38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O7" s="38" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="P7" s="38" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="Q7" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="R7" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="S7" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="T7" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="U7" s="39"/>
+    </row>
+    <row r="8" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="39"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I8" s="38" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="J8" s="39"/>
+      <c r="K8" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L8" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M8" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N8" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O8" s="38" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P8" s="38" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="Q8" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="R8" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="S8" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="T8" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="U8" s="39"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="39"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H9" s="38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I9" s="38" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="J9" s="39"/>
+      <c r="K9" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L9" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M9" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N9" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O9" s="38" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P9" s="38" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Q9" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="R9" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="S9" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="T9" s="39"/>
+      <c r="U9" s="39"/>
+    </row>
+    <row r="10" customFormat="false" ht="28.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="39"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="H10" s="38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I10" s="38" t="n">
+        <v>1.647</v>
+      </c>
+      <c r="J10" s="39"/>
+      <c r="K10" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L10" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="M10" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N10" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O10" s="38" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="P10" s="41" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q10" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="R10" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="S10" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="T10" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="U10" s="39"/>
+    </row>
+    <row r="11" customFormat="false" ht="26.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="39"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="H11" s="38" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="I11" s="38" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="J11" s="39"/>
+      <c r="K11" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L11" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M11" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N11" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O11" s="38" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="P11" s="38" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="S11" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="T11" s="39"/>
+      <c r="U11" s="39"/>
+    </row>
+    <row r="12" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="39"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="H12" s="38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I12" s="38" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="J12" s="39"/>
+      <c r="K12" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L12" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M12" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N12" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O12" s="38" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P12" s="38" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Q12" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="R12" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="S12" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="T12" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="U12" s="39"/>
+    </row>
+    <row r="13" customFormat="false" ht="26.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="39"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H13" s="39"/>
+      <c r="I13" s="38" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="J13" s="39"/>
+      <c r="K13" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L13" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M13" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N13" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O13" s="38" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="P13" s="38" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="39"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="39"/>
+    </row>
+    <row r="14" customFormat="false" ht="25.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="39"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H14" s="38" t="n">
+        <v>9.8</v>
+      </c>
+      <c r="I14" s="38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J14" s="39"/>
+      <c r="K14" s="38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="L14" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="M14" s="38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N14" s="38" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O14" s="38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P14" s="41" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q14" s="39"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="T14" s="39"/>
+      <c r="U14" s="39"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="39"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="39"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="39"/>
+      <c r="S16" s="39"/>
+      <c r="T16" s="39"/>
+      <c r="U16" s="39"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="39"/>
+      <c r="R17" s="39"/>
+      <c r="S17" s="39"/>
+      <c r="T17" s="39"/>
+      <c r="U17" s="39"/>
+    </row>
+    <row r="18" customFormat="false" ht="26.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H18" s="38" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I18" s="38" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J18" s="39"/>
+      <c r="K18" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="L18" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="M18" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N18" s="38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O18" s="38" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="P18" s="41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="T18" s="39"/>
+      <c r="U18" s="39"/>
+    </row>
+    <row r="19" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" s="38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I19" s="38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J19" s="39"/>
+      <c r="K19" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L19" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M19" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N19" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O19" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P19" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="39"/>
+      <c r="S19" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="T19" s="39"/>
+      <c r="U19" s="39"/>
+    </row>
+    <row r="20" customFormat="false" ht="21.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="E20" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H20" s="38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I20" s="38" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="J20" s="39"/>
+      <c r="K20" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="L20" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="M20" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N20" s="38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O20" s="38" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="P20" s="38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="39"/>
+      <c r="S20" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="T20" s="39"/>
+      <c r="U20" s="39"/>
+    </row>
+    <row r="21" customFormat="false" ht="22.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="H21" s="38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I21" s="38" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="J21" s="39"/>
+      <c r="K21" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L21" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="M21" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N21" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O21" s="38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P21" s="38" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="T21" s="39"/>
+      <c r="U21" s="39"/>
+    </row>
+    <row r="22" customFormat="false" ht="22.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H22" s="38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I22" s="38" t="n">
+        <v>3.118</v>
+      </c>
+      <c r="J22" s="39"/>
+      <c r="K22" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L22" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M22" s="38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N22" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O22" s="38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="P22" s="41" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="39"/>
+      <c r="S22" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="T22" s="39"/>
+      <c r="U22" s="39"/>
+    </row>
+    <row r="23" customFormat="false" ht="22.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="39"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H23" s="38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I23" s="38" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="J23" s="39"/>
+      <c r="K23" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L23" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M23" s="38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N23" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O23" s="38" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P23" s="41" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="39"/>
+      <c r="S23" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="T23" s="39"/>
+      <c r="U23" s="39"/>
+    </row>
+    <row r="24" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="39"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="E24" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="H24" s="38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I24" s="38" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="J24" s="39"/>
+      <c r="K24" s="38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L24" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M24" s="38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N24" s="38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O24" s="38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P24" s="41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
+      <c r="S24" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="T24" s="39"/>
+      <c r="U24" s="39"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="39"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="39"/>
+      <c r="R25" s="39"/>
+      <c r="S25" s="39"/>
+      <c r="T25" s="39"/>
+      <c r="U25" s="39"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="39"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="39"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="39"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="39"/>
+      <c r="R27" s="39"/>
+      <c r="S27" s="39"/>
+      <c r="T27" s="39"/>
+      <c r="U27" s="39"/>
+    </row>
+    <row r="28" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="39"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H28" s="38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I28" s="38" t="n">
+        <v>2.038</v>
+      </c>
+      <c r="J28" s="39"/>
+      <c r="K28" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L28" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="M28" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N28" s="38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O28" s="38" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="P28" s="41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="39"/>
+      <c r="S28" s="39"/>
+      <c r="T28" s="39"/>
+      <c r="U28" s="39"/>
+    </row>
+    <row r="29" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="39"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H29" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="38" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J29" s="39"/>
+      <c r="K29" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L29" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M29" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N29" s="38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O29" s="38" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P29" s="38" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="39"/>
+      <c r="S29" s="39"/>
+      <c r="T29" s="39"/>
+      <c r="U29" s="39"/>
+    </row>
+    <row r="30" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="39"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="E30" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H30" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" s="38" t="n">
+        <v>0.687</v>
+      </c>
+      <c r="J30" s="39"/>
+      <c r="K30" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L30" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="M30" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N30" s="38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O30" s="38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P30" s="38" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q30" s="39"/>
+      <c r="R30" s="39"/>
+      <c r="S30" s="39"/>
+      <c r="T30" s="39"/>
+      <c r="U30" s="39"/>
+    </row>
+    <row r="31" customFormat="false" ht="25.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="39"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D31" s="38" t="s">
+        <v>244</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H31" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J31" s="39"/>
+      <c r="K31" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="L31" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="M31" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N31" s="38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O31" s="38" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P31" s="38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q31" s="39"/>
+      <c r="R31" s="39"/>
+      <c r="S31" s="39"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="39"/>
+    </row>
+    <row r="32" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="39"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D32" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="E32" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H32" s="38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I32" s="38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J32" s="39"/>
+      <c r="K32" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L32" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M32" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N32" s="38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O32" s="38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P32" s="38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q32" s="39"/>
+      <c r="R32" s="39"/>
+      <c r="S32" s="39"/>
+      <c r="T32" s="39"/>
+      <c r="U32" s="39"/>
+    </row>
+    <row r="33" customFormat="false" ht="28.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="39"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D33" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="E33" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="G33" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H33" s="38" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I33" s="38" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="J33" s="39"/>
+      <c r="K33" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L33" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M33" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N33" s="38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O33" s="38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P33" s="41" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q33" s="39"/>
+      <c r="R33" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="S33" s="39"/>
+      <c r="T33" s="39"/>
+      <c r="U33" s="39"/>
+    </row>
+    <row r="34" customFormat="false" ht="22.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="39"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D34" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="E34" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="G34" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="H34" s="38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I34" s="38" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="J34" s="39"/>
+      <c r="K34" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L34" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="M34" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N34" s="38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O34" s="38" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="P34" s="38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q34" s="39"/>
+      <c r="R34" s="39"/>
+      <c r="S34" s="39"/>
+      <c r="T34" s="39"/>
+      <c r="U34" s="39"/>
+    </row>
+    <row r="35" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="39"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D35" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="E35" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="G35" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H35" s="38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I35" s="38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J35" s="39"/>
+      <c r="K35" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="L35" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M35" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N35" s="38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O35" s="38" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P35" s="38" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q35" s="39"/>
+      <c r="R35" s="39"/>
+      <c r="S35" s="39"/>
+      <c r="T35" s="39"/>
+      <c r="U35" s="39"/>
+    </row>
+    <row r="36" customFormat="false" ht="26.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="39"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D36" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="E36" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="G36" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H36" s="38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I36" s="38" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="J36" s="39"/>
+      <c r="K36" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L36" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="M36" s="38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N36" s="38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O36" s="38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P36" s="38" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="Q36" s="39"/>
+      <c r="R36" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="S36" s="39"/>
+      <c r="T36" s="39"/>
+      <c r="U36" s="39"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="39"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="39"/>
+      <c r="Q37" s="39"/>
+      <c r="R37" s="39"/>
+      <c r="S37" s="39"/>
+      <c r="T37" s="39"/>
+      <c r="U37" s="39"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="39"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="39"/>
+      <c r="Q38" s="39"/>
+      <c r="R38" s="39"/>
+      <c r="S38" s="39"/>
+      <c r="T38" s="39"/>
+      <c r="U38" s="39"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="39"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="39"/>
+      <c r="R39" s="39"/>
+      <c r="S39" s="39"/>
+      <c r="T39" s="39"/>
+      <c r="U39" s="39"/>
+    </row>
+    <row r="40" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="39"/>
+      <c r="B40" s="39"/>
+      <c r="C40" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D40" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="E40" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H40" s="38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I40" s="38" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J40" s="39"/>
+      <c r="K40" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L40" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="M40" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="O40" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="P40" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q40" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="R40" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="S40" s="39"/>
+      <c r="T40" s="39"/>
+      <c r="U40" s="39"/>
+    </row>
+    <row r="41" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="39"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D41" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="E41" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="G41" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="H41" s="38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I41" s="38" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J41" s="39"/>
+      <c r="K41" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L41" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M41" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="39"/>
+      <c r="R41" s="39"/>
+      <c r="S41" s="39"/>
+      <c r="T41" s="39"/>
+      <c r="U41" s="39"/>
+    </row>
+    <row r="42" customFormat="false" ht="34.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="39"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D42" s="38" t="s">
+        <v>260</v>
+      </c>
+      <c r="E42" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="G42" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H42" s="38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I42" s="38" t="n">
+        <v>3.266</v>
+      </c>
+      <c r="J42" s="39"/>
+      <c r="K42" s="38" t="n">
+        <v>2018</v>
+      </c>
+      <c r="L42" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="M42" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O42" s="39"/>
+      <c r="P42" s="39"/>
+      <c r="Q42" s="39"/>
+      <c r="R42" s="38" t="s">
+        <v>262</v>
+      </c>
+      <c r="S42" s="39"/>
+      <c r="T42" s="39"/>
+      <c r="U42" s="39"/>
+    </row>
+    <row r="43" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="39"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D43" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="E43" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="G43" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H43" s="38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I43" s="39"/>
+      <c r="J43" s="39"/>
+      <c r="K43" s="39"/>
+      <c r="L43" s="39"/>
+      <c r="M43" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="39"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="39"/>
+      <c r="Q43" s="39"/>
+      <c r="R43" s="39"/>
+      <c r="S43" s="39"/>
+      <c r="T43" s="39"/>
+      <c r="U43" s="39"/>
+    </row>
+    <row r="44" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="39"/>
+      <c r="B44" s="39"/>
+      <c r="C44" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D44" s="38" t="s">
+        <v>264</v>
+      </c>
+      <c r="E44" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="G44" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H44" s="38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I44" s="38" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="J44" s="39"/>
+      <c r="K44" s="38" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L44" s="39"/>
+      <c r="M44" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="39"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="39"/>
+      <c r="Q44" s="39"/>
+      <c r="R44" s="39"/>
+      <c r="S44" s="39"/>
+      <c r="T44" s="39"/>
+      <c r="U44" s="39"/>
+    </row>
+    <row r="45" customFormat="false" ht="25.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="39"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D45" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="E45" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="G45" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H45" s="38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I45" s="38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J45" s="39"/>
+      <c r="K45" s="38" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L45" s="39"/>
+      <c r="M45" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="39"/>
+      <c r="O45" s="39"/>
+      <c r="P45" s="39"/>
+      <c r="Q45" s="39"/>
+      <c r="R45" s="39"/>
+      <c r="S45" s="39"/>
+      <c r="T45" s="39"/>
+      <c r="U45" s="39"/>
+    </row>
+    <row r="46" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="39"/>
+      <c r="B46" s="39"/>
+      <c r="C46" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D46" s="38" t="s">
+        <v>266</v>
+      </c>
+      <c r="E46" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="G46" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H46" s="38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I46" s="38" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J46" s="39"/>
+      <c r="K46" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L46" s="40" t="s">
+        <v>267</v>
+      </c>
+      <c r="M46" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="39"/>
+      <c r="O46" s="39"/>
+      <c r="P46" s="39"/>
+      <c r="Q46" s="39"/>
+      <c r="R46" s="39"/>
+      <c r="S46" s="39"/>
+      <c r="T46" s="39"/>
+      <c r="U46" s="39"/>
+    </row>
+    <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="39"/>
+      <c r="B47" s="39"/>
+      <c r="C47" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D47" s="38" t="s">
+        <v>268</v>
+      </c>
+      <c r="E47" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="G47" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="H47" s="38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I47" s="38" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="J47" s="39"/>
+      <c r="K47" s="38" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L47" s="39"/>
+      <c r="M47" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="39"/>
+      <c r="O47" s="39"/>
+      <c r="P47" s="39"/>
+      <c r="Q47" s="39"/>
+      <c r="R47" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="S47" s="39"/>
+      <c r="T47" s="39"/>
+      <c r="U47" s="39"/>
+    </row>
+    <row r="48" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="39"/>
+      <c r="B48" s="39"/>
+      <c r="C48" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D48" s="38" t="s">
+        <v>270</v>
+      </c>
+      <c r="E48" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="G48" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H48" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="I48" s="38" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="J48" s="39"/>
+      <c r="K48" s="38" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L48" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="M48" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="39"/>
+      <c r="O48" s="39"/>
+      <c r="P48" s="39"/>
+      <c r="Q48" s="39"/>
+      <c r="R48" s="39"/>
+      <c r="S48" s="39"/>
+      <c r="T48" s="39"/>
+      <c r="U48" s="39"/>
+    </row>
+    <row r="49" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="39"/>
+      <c r="B49" s="39"/>
+      <c r="C49" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D49" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="E49" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>272</v>
+      </c>
+      <c r="G49" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="H49" s="38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I49" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="39"/>
+      <c r="K49" s="38" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L49" s="39"/>
+      <c r="M49" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="39"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="39"/>
+      <c r="Q49" s="39"/>
+      <c r="R49" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="S49" s="39"/>
+      <c r="T49" s="39"/>
+      <c r="U49" s="39"/>
+    </row>
+    <row r="50" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="39"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D50" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="E50" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>272</v>
+      </c>
+      <c r="G50" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="H50" s="38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I50" s="38" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="J50" s="39"/>
+      <c r="K50" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L50" s="39"/>
+      <c r="M50" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="39"/>
+      <c r="O50" s="39"/>
+      <c r="P50" s="39"/>
+      <c r="Q50" s="39"/>
+      <c r="R50" s="39"/>
+      <c r="S50" s="39"/>
+      <c r="T50" s="39"/>
+      <c r="U50" s="39"/>
+    </row>
+    <row r="51" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="39"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D51" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="E51" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="G51" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="H51" s="38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I51" s="38" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="J51" s="39"/>
+      <c r="K51" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L51" s="39"/>
+      <c r="M51" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="39"/>
+      <c r="O51" s="39"/>
+      <c r="P51" s="39"/>
+      <c r="Q51" s="39"/>
+      <c r="R51" s="39"/>
+      <c r="S51" s="39"/>
+      <c r="T51" s="39"/>
+      <c r="U51" s="39"/>
+    </row>
+    <row r="52" customFormat="false" ht="21.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="39"/>
+      <c r="B52" s="39"/>
+      <c r="C52" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D52" s="38" t="s">
+        <v>276</v>
+      </c>
+      <c r="E52" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F52" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="G52" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="H52" s="38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I52" s="38" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="J52" s="39"/>
+      <c r="K52" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L52" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="M52" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="39"/>
+      <c r="O52" s="39"/>
+      <c r="P52" s="39"/>
+      <c r="Q52" s="39"/>
+      <c r="R52" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="S52" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="T52" s="39"/>
+      <c r="U52" s="39"/>
+    </row>
+    <row r="53" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="39"/>
+      <c r="B53" s="39"/>
+      <c r="C53" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>280</v>
+      </c>
+      <c r="E53" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F53" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="G53" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="H53" s="38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I53" s="38" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="J53" s="39"/>
+      <c r="K53" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L53" s="39"/>
+      <c r="M53" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="39"/>
+      <c r="O53" s="39"/>
+      <c r="P53" s="39"/>
+      <c r="Q53" s="39"/>
+      <c r="R53" s="39"/>
+      <c r="S53" s="39"/>
+      <c r="T53" s="39"/>
+      <c r="U53" s="39"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="39"/>
+      <c r="B54" s="39"/>
+      <c r="C54" s="38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D54" s="39"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="39"/>
+      <c r="K54" s="39"/>
+      <c r="L54" s="39"/>
+      <c r="M54" s="39"/>
+      <c r="N54" s="39"/>
+      <c r="O54" s="39"/>
+      <c r="P54" s="39"/>
+      <c r="Q54" s="39"/>
+      <c r="R54" s="39"/>
+      <c r="S54" s="39"/>
+      <c r="T54" s="39"/>
+      <c r="U54" s="39"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="S5" r:id="rId1" display="SVV årsrapport 2010"/>
+    <hyperlink ref="T5" r:id="rId2" display="SVV årsrapport 2011"/>
+    <hyperlink ref="U5" r:id="rId3" display="St.prp. nr. 79 - regjeringen.no"/>
+    <hyperlink ref="S6" r:id="rId4" display="SVV årsrapport 2010"/>
+    <hyperlink ref="T6" r:id="rId5" display="E18 Bjørvikatunnelen"/>
+    <hyperlink ref="U6" r:id="rId6" display="St.prp. nr. 50"/>
+    <hyperlink ref="S7" r:id="rId7" display="SVV årsrapport 2010"/>
+    <hyperlink ref="T7" r:id="rId8" display="SVV årsrapport 2011"/>
+    <hyperlink ref="S8" r:id="rId9" display="SVV årsrapport 2010"/>
+    <hyperlink ref="T8" r:id="rId10" display="SVV årsrapport 2011"/>
+    <hyperlink ref="S9" r:id="rId11" display="SVV årsrapport 2010"/>
+    <hyperlink ref="S10" r:id="rId12" display="SVV årsrapport 2010"/>
+    <hyperlink ref="T10" r:id="rId13" display="SVV årsrapport 2011"/>
+    <hyperlink ref="S11" r:id="rId14" display="SVV årsrapport 2010"/>
+    <hyperlink ref="S12" r:id="rId15" display="SVV årsrapport 2010"/>
+    <hyperlink ref="T12" r:id="rId16" display="SVV årsrapport 2011"/>
+    <hyperlink ref="R40" r:id="rId17" display="https://anlegg.bygg.no/bygg/her-kan-du-kjore-nye-e39/502482"/>
+    <hyperlink ref="S52" r:id="rId18" display="https://www.ifinnmark.no/sorsia/veisprekk-pa-15-mill/s/1-65-6955927"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>